--- a/results/Начальные_данные.xlsx
+++ b/results/Начальные_данные.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.43</v>
+        <v>0.433333</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.36</v>
+        <v>0.366666</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">

--- a/results/Начальные_данные.xlsx
+++ b/results/Начальные_данные.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.433333</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.366666</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/results/Начальные_данные.xlsx
+++ b/results/Начальные_данные.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">

--- a/results/Начальные_данные.xlsx
+++ b/results/Начальные_данные.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
